--- a/cellstocks/exports/roster.xlsx
+++ b/cellstocks/exports/roster.xlsx
@@ -74645,7 +74645,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -74665,7 +74665,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -74675,7 +74675,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+15</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -74685,12 +74685,12 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-31</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -74700,14 +74700,14 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t xml:space="preserve">G3</t>
+          <t xml:space="preserve">G2</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LnCap Canada</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -74727,17 +74727,17 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+15</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -74747,12 +74747,12 @@
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2025-07-31</t>
         </is>
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">31-07-25</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
@@ -74769,7 +74769,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -74789,17 +74789,17 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -74809,12 +74809,12 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-20</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t xml:space="preserve">20-02-26</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
@@ -74861,7 +74861,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+17</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -74871,12 +74871,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2026-02-20</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">20-02-26</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
@@ -74923,7 +74923,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+6</t>
+          <t xml:space="preserve">p+17</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -74933,12 +74933,12 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-28</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t xml:space="preserve">28-11-25</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
@@ -74948,14 +74948,14 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -74980,12 +74980,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+20</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -74995,12 +74995,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-26</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-05-26</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -75010,7 +75010,7 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t xml:space="preserve">G4</t>
+          <t xml:space="preserve">G3</t>
         </is>
       </c>
     </row>
@@ -75047,7 +75047,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+9</t>
+          <t xml:space="preserve">p+6</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -75057,12 +75057,12 @@
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-20</t>
+          <t xml:space="preserve">2025-11-28</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t xml:space="preserve">20-02-26</t>
+          <t xml:space="preserve">28-11-25</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
@@ -75079,7 +75079,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -75099,17 +75099,17 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+17</t>
+          <t xml:space="preserve">p+20</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -75119,12 +75119,12 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2026-05-26</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">26-05-26</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
@@ -75141,7 +75141,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G1</t>
+          <t xml:space="preserve">LnCap Canada</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -75171,7 +75171,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+2</t>
+          <t xml:space="preserve">p+9</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -75181,12 +75181,12 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-30</t>
+          <t xml:space="preserve">2026-02-20</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t xml:space="preserve">30-05-25</t>
+          <t xml:space="preserve">20-02-26</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
@@ -75196,24 +75196,14 @@
       </c>
       <c r="L262" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
-        </is>
-      </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">myco -</t>
-        </is>
-      </c>
-      <c r="N262" t="inlineStr">
-        <is>
-          <t xml:space="preserve">myco-negative</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G4</t>
+          <t xml:space="preserve">LnCap Canada</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -75243,22 +75233,22 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+17</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -75268,7 +75258,7 @@
       </c>
       <c r="L263" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
     </row>
@@ -75305,7 +75295,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -75315,12 +75305,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-05-26</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -75330,14 +75320,14 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t xml:space="preserve">G5</t>
+          <t xml:space="preserve">G4</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada</t>
+          <t xml:space="preserve">LnCap Canada V1G1</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -75367,7 +75357,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+17</t>
+          <t xml:space="preserve">p+2</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -75377,12 +75367,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-05-30</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">30-05-25</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -75393,13 +75383,23 @@
       <c r="L265" t="inlineStr">
         <is>
           <t xml:space="preserve">G5</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">myco -</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">myco-negative</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada</t>
+          <t xml:space="preserve">LnCap Canada V1G4</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -75429,22 +75429,22 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+15</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-31</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -75454,14 +75454,14 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G3</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -75481,7 +75481,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -75491,22 +75491,22 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">18-05-26</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -75516,14 +75516,14 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">LnCap Canada</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -75543,7 +75543,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -75553,7 +75553,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p+17</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -75563,12 +75563,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-05-26</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -75578,17 +75578,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t xml:space="preserve">G6</t>
-        </is>
-      </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">to-do box / thaw</t>
-        </is>
-      </c>
-      <c r="N268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">to-do</t>
+          <t xml:space="preserve">G5</t>
         </is>
       </c>
     </row>
@@ -75625,7 +75615,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+17</t>
+          <t xml:space="preserve">p+15</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -75635,12 +75625,12 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-27</t>
+          <t xml:space="preserve">2025-07-31</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t xml:space="preserve">27-10-25</t>
+          <t xml:space="preserve">31-07-25</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -75657,7 +75647,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t xml:space="preserve">LCC-V 99.17%</t>
+          <t xml:space="preserve">LnCap Canada V1G3</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -75687,22 +75677,22 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-30</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t xml:space="preserve">30-05-25</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -75712,14 +75702,14 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada V1G2</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -75739,7 +75729,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -75749,22 +75739,22 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t xml:space="preserve">p41</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-19</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t xml:space="preserve">19-05-25</t>
+          <t xml:space="preserve">18-05-26</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -75774,14 +75764,24 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
+          <t xml:space="preserve">G6</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to-do box / thaw</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to-do</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LnCap Canada</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -75801,17 +75801,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+24</t>
+          <t xml:space="preserve">p+17</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -75821,12 +75821,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-22</t>
+          <t xml:space="preserve">2025-10-27</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-05-26</t>
+          <t xml:space="preserve">27-10-25</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -75836,24 +75836,14 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t xml:space="preserve">G7</t>
-        </is>
-      </c>
-      <c r="M272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
+          <t xml:space="preserve">G6</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #2 98%</t>
+          <t xml:space="preserve">LCC-V 99.17%</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -75883,22 +75873,22 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">p24</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-11-15</t>
+          <t xml:space="preserve">2025-05-30</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t xml:space="preserve">15-11-25</t>
+          <t xml:space="preserve">30-05-25</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -75915,7 +75905,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">LnCap Canada V1G2</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -75935,32 +75925,32 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p41</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
+          <t xml:space="preserve">2025-05-19</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">19-05-25</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -75970,24 +75960,14 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
-        </is>
-      </c>
-      <c r="M274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
-        </is>
-      </c>
-      <c r="N274" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select E</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -76012,22 +75992,27 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unknown</t>
+          <t xml:space="preserve">2026-05-22</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22-05-26</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -76037,14 +76022,24 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
+          <t xml:space="preserve">G7</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNC478 #2 98%</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -76064,32 +76059,32 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+25</t>
+          <t xml:space="preserve">p24</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-22</t>
+          <t xml:space="preserve">2025-11-15</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-05-26</t>
+          <t xml:space="preserve">15-11-25</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -76099,24 +76094,14 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">G8</t>
-        </is>
-      </c>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
-        </is>
-      </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
+          <t xml:space="preserve">G7</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #1</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -76136,32 +76121,32 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t xml:space="preserve">p23</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
@@ -76172,13 +76157,23 @@
       <c r="L277" t="inlineStr">
         <is>
           <t xml:space="preserve">G8</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP1</t>
+          <t xml:space="preserve">LnCapCASPEX no select E</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -76203,27 +76198,22 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+21</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-04</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4/6/2026</t>
+          <t xml:space="preserve">Unknown</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
@@ -76233,24 +76223,14 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
-        </is>
-      </c>
-      <c r="M278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -76275,27 +76255,27 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+25</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-22</t>
+          <t xml:space="preserve">2026-05-22</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-04-25</t>
+          <t xml:space="preserve">22-05-26</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
@@ -76305,14 +76285,24 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
+          <t xml:space="preserve">G8</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">LNC478 #1</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -76332,32 +76322,32 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+25</t>
+          <t xml:space="preserve">p23</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-22</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t xml:space="preserve">22-05-26</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -76367,24 +76357,14 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">G9</t>
-        </is>
-      </c>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-</t>
-        </is>
-      </c>
-      <c r="N280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">chip-negative</t>
+          <t xml:space="preserve">G8</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNC478 #3</t>
+          <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -76404,32 +76384,32 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">p23</t>
+          <t xml:space="preserve">p+21</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-12-12</t>
+          <t xml:space="preserve">2026-06-04</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/12/2025</t>
+          <t xml:space="preserve">4/6/2026</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -76440,23 +76420,33 @@
       <c r="L281" t="inlineStr">
         <is>
           <t xml:space="preserve">G9</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g2</t>
+          <t xml:space="preserve">LnCapCASPEX no select +P+D #1</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -76466,32 +76456,32 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t xml:space="preserve">p16</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-21</t>
+          <t xml:space="preserve">2025-04-22</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-05-25</t>
+          <t xml:space="preserve">22-04-25</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -76501,24 +76491,24 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LNCX gP2</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -76528,32 +76518,32 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p+25</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-05-22</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">22-05-26</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
@@ -76563,19 +76553,29 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G9</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chip-negative</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LNC478 #3</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -76585,7 +76585,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
@@ -76600,7 +76600,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p23</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -76610,12 +76610,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-26</t>
+          <t xml:space="preserve">2025-12-12</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-03-26</t>
+          <t xml:space="preserve">12/12/2025</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
@@ -76625,29 +76625,29 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t xml:space="preserve">H1</t>
+          <t xml:space="preserve">G9</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK FOXA1 KO g2</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
@@ -76657,12 +76657,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">p9</t>
+          <t xml:space="preserve">p16</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -76672,12 +76672,12 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-10-07</t>
+          <t xml:space="preserve">2025-05-21</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t xml:space="preserve">7/10/2025</t>
+          <t xml:space="preserve">21-05-25</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
@@ -76694,7 +76694,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK JUN1 KO g2</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -76704,7 +76704,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -76719,12 +76719,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t xml:space="preserve">p13</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -76734,12 +76734,12 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-12-13</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t xml:space="preserve">13-12-23</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
@@ -76749,29 +76749,29 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
@@ -76781,12 +76781,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -76796,12 +76796,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-03-26</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">26-03-26</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
@@ -76811,14 +76811,14 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -76838,7 +76838,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -76848,7 +76848,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p9</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -76858,12 +76858,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-24</t>
+          <t xml:space="preserve">2025-10-07</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-26</t>
+          <t xml:space="preserve">7/10/2025</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -76873,14 +76873,14 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap (m1) no sort</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -76895,12 +76895,12 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -76910,7 +76910,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">p10</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -76920,12 +76920,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-13</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t xml:space="preserve">13-03-26</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -76935,14 +76935,14 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t xml:space="preserve">H2</t>
+          <t xml:space="preserve">H1</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g2</t>
+          <t xml:space="preserve">HEK JUN1 KO g2</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -76972,7 +76972,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p13</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -76982,12 +76982,12 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-21</t>
+          <t xml:space="preserve">2023-12-13</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-07-25</t>
+          <t xml:space="preserve">13-12-23</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
@@ -76997,14 +76997,14 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -77034,7 +77034,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">p43</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -77044,12 +77044,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
@@ -77059,7 +77059,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
     </row>
@@ -77121,21 +77121,21 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
+          <t xml:space="preserve">LuCap (m1) no sort</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LuCap35CR</t>
-        </is>
-      </c>
       <c r="C293" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -77143,7 +77143,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -77168,12 +77168,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-16</t>
+          <t xml:space="preserve">2026-03-13</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-03-26</t>
+          <t xml:space="preserve">13-03-26</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
@@ -77183,44 +77183,44 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">H3</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g1</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -77230,12 +77230,12 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-21</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-07-25</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
@@ -77245,14 +77245,14 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H2</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">HEK RFX KO g2</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -77262,7 +77262,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -77277,12 +77277,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -77292,12 +77292,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2025-07-21</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">21-07-25</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
@@ -77307,44 +77307,44 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p43</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -77354,12 +77354,12 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-05-26</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
@@ -77369,21 +77369,21 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
+          <t xml:space="preserve">LUCX</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
           <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
-      <c r="B297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LuCap35CR</t>
-        </is>
-      </c>
       <c r="C297" t="inlineStr">
         <is>
           <t xml:space="preserve">-</t>
@@ -77396,7 +77396,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -77406,7 +77406,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -77416,12 +77416,12 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-12</t>
+          <t xml:space="preserve">2026-04-24</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/6/2026</t>
+          <t xml:space="preserve">24-04-26</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
@@ -77431,29 +77431,29 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">H4</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g1</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -77463,12 +77463,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p10</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -77478,12 +77478,12 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-21</t>
+          <t xml:space="preserve">2026-03-16</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-05-25</t>
+          <t xml:space="preserve">16-03-26</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
@@ -77493,19 +77493,19 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B GFP</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -77515,12 +77515,12 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -77530,7 +77530,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -77540,12 +77540,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">2026-09-15</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -77555,39 +77555,39 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H3</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">HEK FOXA1 KO g1</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -77602,12 +77602,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2025-07-21</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-05-26</t>
+          <t xml:space="preserve">21-07-25</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -77617,19 +77617,19 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -77639,7 +77639,7 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -77654,7 +77654,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t xml:space="preserve">p11</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -77664,12 +77664,12 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-12</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/6/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
@@ -77679,39 +77679,39 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t xml:space="preserve">H5</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK RFX KO g1</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -77726,12 +77726,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-21</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-07-25</t>
+          <t xml:space="preserve">18-05-26</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
@@ -77741,19 +77741,19 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CASPEX gNT</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -77763,37 +77763,37 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-10</t>
+          <t xml:space="preserve">2026-06-12</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/2/2026</t>
+          <t xml:space="preserve">12/6/2026</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
@@ -77803,44 +77803,44 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H4</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">HEK HOXB6 KO g1</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -77850,12 +77850,12 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-18</t>
+          <t xml:space="preserve">2025-05-21</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-05-26</t>
+          <t xml:space="preserve">21-05-25</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
@@ -77865,19 +77865,19 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">HEK ATP7B GFP</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -77887,22 +77887,22 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">p20</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -77912,12 +77912,12 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-12</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/6/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
@@ -77927,44 +77927,44 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t xml:space="preserve">H6</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK SPEN KO g2</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -77974,12 +77974,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-21</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-07-25</t>
+          <t xml:space="preserve">18-05-26</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
@@ -77989,29 +77989,29 @@
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -78021,12 +78021,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p11</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -78036,12 +78036,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-06-12</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">12/6/2026</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
@@ -78051,44 +78051,44 @@
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H5</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX</t>
+          <t xml:space="preserve">HEK RFX KO g1</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">p19</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -78098,12 +78098,12 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2025-07-21</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">21-07-25</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
@@ -78113,29 +78113,19 @@
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
-        </is>
-      </c>
-      <c r="M308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">to-do box / thaw</t>
-        </is>
-      </c>
-      <c r="N308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">to-do</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1</t>
+          <t xml:space="preserve">HEK CASPEX gNT</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -78145,7 +78135,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -78155,27 +78145,27 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">p20</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-12</t>
+          <t xml:space="preserve">2026-02-10</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/6/2026</t>
+          <t xml:space="preserve">10/2/2026</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
@@ -78185,44 +78175,44 @@
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">H7</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK HOXB6 KO g2</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -78232,12 +78222,12 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-21</t>
+          <t xml:space="preserve">2026-05-18</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-05-25</t>
+          <t xml:space="preserve">18-05-26</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
@@ -78247,44 +78237,44 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK APEX1 OX</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">p21</t>
+          <t xml:space="preserve">p20</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -78294,12 +78284,12 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-06</t>
+          <t xml:space="preserve">2026-06-12</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t xml:space="preserve">6/2/2026</t>
+          <t xml:space="preserve">12/6/2026</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
@@ -78309,44 +78299,44 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H6</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP1</t>
+          <t xml:space="preserve">HEK SPEN KO g2</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t xml:space="preserve">LuCap35CR</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">CR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">p20</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -78356,12 +78346,12 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-12</t>
+          <t xml:space="preserve">2025-07-21</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t xml:space="preserve">12/6/2026</t>
+          <t xml:space="preserve">21-07-25</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
@@ -78371,14 +78361,14 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">H8</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 ATP7B OX</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -78408,7 +78398,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -78418,12 +78408,12 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-01-05</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/1/2024</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
@@ -78433,34 +78423,34 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 OX</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -78470,7 +78460,7 @@
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">p28</t>
+          <t xml:space="preserve">p19</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -78480,12 +78470,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2026-07-31</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">31-07-26</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -78495,14 +78485,24 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to-do box / thaw</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">to-do</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUCX gP2</t>
+          <t xml:space="preserve">LUCX gP1</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -78527,7 +78527,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -78557,14 +78557,14 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t xml:space="preserve">H9</t>
+          <t xml:space="preserve">H7</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g2</t>
+          <t xml:space="preserve">HEK HOXB6 KO g2</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -78574,7 +78574,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -78619,59 +78619,59 @@
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">HEK APEX1 OX</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+3</t>
+          <t xml:space="preserve">p21</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-16</t>
+          <t xml:space="preserve">2026-02-06</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-05-25</t>
+          <t xml:space="preserve">6/2/2026</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
@@ -78681,19 +78681,19 @@
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh1</t>
+          <t xml:space="preserve">LUCX gP1</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -78703,17 +78703,17 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">gP1</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -78728,12 +78728,12 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-02</t>
+          <t xml:space="preserve">2026-06-12</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/2/2026</t>
+          <t xml:space="preserve">12/6/2026</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
@@ -78743,24 +78743,24 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H8</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada</t>
+          <t xml:space="preserve">HEK FOXA1 KO g1</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -78775,27 +78775,27 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+14</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-10</t>
+          <t xml:space="preserve">2024-01-05</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/3/2026</t>
+          <t xml:space="preserve">5/1/2024</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
@@ -78805,14 +78805,14 @@
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">I1</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 OX</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -78822,7 +78822,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -78837,12 +78837,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p28</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -78852,12 +78852,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-21</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-07-25</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
@@ -78867,19 +78867,19 @@
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">LUCX gP2</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LuCap35CR</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -78889,7 +78889,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">CR</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
@@ -78899,27 +78899,27 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">gP2</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p20</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-06-12</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">12/6/2026</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -78929,14 +78929,14 @@
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">H9</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B-GFP</t>
+          <t xml:space="preserve">HEK GATA6 KO g2</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -78946,7 +78946,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -78961,12 +78961,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">p31</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -78976,12 +78976,12 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-26</t>
+          <t xml:space="preserve">2025-05-21</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-01-26</t>
+          <t xml:space="preserve">21-05-25</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -78991,19 +78991,19 @@
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -79013,7 +79013,7 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -79023,27 +79023,27 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">p12</t>
+          <t xml:space="preserve">p+3</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-30</t>
+          <t xml:space="preserve">2025-05-16</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t xml:space="preserve">30-03-26</t>
+          <t xml:space="preserve">16-05-25</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -79053,14 +79053,14 @@
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">I2</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK NRF2 KO g2</t>
+          <t xml:space="preserve">HEK E2F1 sh1</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -79070,7 +79070,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -79085,12 +79085,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">p17</t>
+          <t xml:space="preserve">p20</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -79100,12 +79100,12 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-07-21</t>
+          <t xml:space="preserve">2026-02-02</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-07-25</t>
+          <t xml:space="preserve">2/2/2026</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
@@ -79115,19 +79115,19 @@
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">LnCap Canada</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -79137,22 +79137,22 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+14</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -79162,12 +79162,12 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-10</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">10/3/2026</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
@@ -79177,14 +79177,14 @@
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I1</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK E2F1 sh1</t>
+          <t xml:space="preserve">HEK NRF2 KO g1</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -79194,7 +79194,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -79209,12 +79209,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">sh</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">p20</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -79224,12 +79224,12 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-02-02</t>
+          <t xml:space="preserve">2025-07-21</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2/2/2026</t>
+          <t xml:space="preserve">21-07-25</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
@@ -79239,19 +79239,19 @@
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -79261,7 +79261,7 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -79271,12 +79271,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+17</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -79286,12 +79286,12 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-30</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t xml:space="preserve">30-03-26</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
@@ -79301,14 +79301,14 @@
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t xml:space="preserve">I3</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK FOXA1 KO g2</t>
+          <t xml:space="preserve">HEK ATP7B-GFP</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -79318,7 +79318,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -79333,12 +79333,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">g2</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">p14</t>
+          <t xml:space="preserve">p31</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -79348,12 +79348,12 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-04-05</t>
+          <t xml:space="preserve">2026-01-26</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t xml:space="preserve">5/4/2024</t>
+          <t xml:space="preserve">26-01-26</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
@@ -79363,19 +79363,19 @@
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -79385,7 +79385,7 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -79395,27 +79395,27 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p12</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">30-03-26</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
@@ -79425,14 +79425,14 @@
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I2</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B-GFP</t>
+          <t xml:space="preserve">HEK NRF2 KO g2</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -79442,7 +79442,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -79457,12 +79457,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">p31</t>
+          <t xml:space="preserve">p17</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -79472,12 +79472,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-26</t>
+          <t xml:space="preserve">2025-07-21</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t xml:space="preserve">26-01-26</t>
+          <t xml:space="preserve">21-07-25</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
@@ -79487,19 +79487,19 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -79509,7 +79509,7 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -79519,12 +79519,12 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+17</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -79534,12 +79534,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-30</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t xml:space="preserve">30-03-26</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
@@ -79549,14 +79549,14 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">I4</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK GATA6 KO g1</t>
+          <t xml:space="preserve">HEK E2F1 sh1</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -79566,7 +79566,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -79581,12 +79581,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">sh</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t xml:space="preserve">p18</t>
+          <t xml:space="preserve">p20</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -79596,12 +79596,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-21</t>
+          <t xml:space="preserve">2026-02-02</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-05-25</t>
+          <t xml:space="preserve">2/2/2026</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
@@ -79611,19 +79611,19 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -79633,7 +79633,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -79643,12 +79643,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+17</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -79658,12 +79658,12 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">30-03-26</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
@@ -79673,14 +79673,14 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I3</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
+          <t xml:space="preserve">HEK FOXA1 KO g2</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -79690,7 +79690,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">OX</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -79705,12 +79705,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1</t>
+          <t xml:space="preserve">g2</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t xml:space="preserve">p42</t>
+          <t xml:space="preserve">p14</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -79720,12 +79720,12 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-24</t>
+          <t xml:space="preserve">2024-04-05</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-03-26</t>
+          <t xml:space="preserve">5/4/2024</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
@@ -79735,19 +79735,19 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -79757,22 +79757,22 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+14</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -79782,12 +79782,12 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-23</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-03-26</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
@@ -79797,14 +79797,14 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">I5</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK CBX3 KO G1</t>
+          <t xml:space="preserve">HEK ATP7B-GFP</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -79814,7 +79814,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t xml:space="preserve">KO</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -79834,7 +79834,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p31</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -79844,12 +79844,12 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-01-26</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">26-01-26</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
@@ -79859,19 +79859,19 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -79881,7 +79881,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -79891,12 +79891,12 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">g1.1</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+4</t>
+          <t xml:space="preserve">p+17</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -79906,12 +79906,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-05-14</t>
+          <t xml:space="preserve">2026-03-30</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t xml:space="preserve">14-05-25</t>
+          <t xml:space="preserve">30-03-26</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -79921,14 +79921,14 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I4</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK GATA6 KO g1</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -79953,27 +79953,27 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+2</t>
+          <t xml:space="preserve">p18</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2025-05-21</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">21-05-25</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -79983,19 +79983,19 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap Canada</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -80005,22 +80005,22 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+14</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -80030,12 +80030,12 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-03-23</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t xml:space="preserve">23-03-26</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
@@ -80045,14 +80045,14 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">I6</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK POU3F3 KO g1</t>
+          <t xml:space="preserve">HEK CBX3 KO g1 plv-GFP</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -80082,7 +80082,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p42</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -80092,12 +80092,12 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2026-03-24</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">24-03-26</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
@@ -80107,19 +80107,19 @@
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap Canada</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -80144,22 +80144,22 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">p?</t>
+          <t xml:space="preserve">p+14</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">unknown</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-03-23</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">23-03-26</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
@@ -80169,14 +80169,14 @@
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I5</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B KO g3</t>
+          <t xml:space="preserve">HEK CBX3 KO G1</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -80201,27 +80201,27 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">g3</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+2</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-04-10</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t xml:space="preserve">10/4/2026</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -80231,19 +80231,19 @@
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gNT</t>
+          <t xml:space="preserve">DuDtxR CASPEX g1.1</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -80253,7 +80253,7 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Par</t>
+          <t xml:space="preserve">DtxR</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -80263,12 +80263,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">g1.1</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+24</t>
+          <t xml:space="preserve">p+4</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -80278,12 +80278,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-18</t>
+          <t xml:space="preserve">2025-05-14</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-06-26</t>
+          <t xml:space="preserve">14-05-25</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -80293,14 +80293,14 @@
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">I7</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATP7B-GFP</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -80310,7 +80310,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -80325,27 +80325,27 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">g3</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t xml:space="preserve">p47</t>
+          <t xml:space="preserve">p+2</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-05-04</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t xml:space="preserve">4/5/2026</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
@@ -80355,19 +80355,19 @@
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuPar50CR+1</t>
+          <t xml:space="preserve">LnCap Canada</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -80377,7 +80377,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t xml:space="preserve">CisR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -80392,22 +80392,22 @@
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">P218</t>
+          <t xml:space="preserve">p+14</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-03-23</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">23-03-26</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
@@ -80417,24 +80417,24 @@
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I6</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t xml:space="preserve">LNCX gP2</t>
+          <t xml:space="preserve">HEK POU3F3 KO g1</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t xml:space="preserve">LnCap</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -80444,32 +80444,32 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">gP2</t>
+          <t xml:space="preserve">g1</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">p+24</t>
+          <t xml:space="preserve">p15</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">relative</t>
+          <t xml:space="preserve">absolute</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-06-18</t>
+          <t xml:space="preserve">2026-01-16</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t xml:space="preserve">18-06-26</t>
+          <t xml:space="preserve">16-01-26</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
@@ -80479,19 +80479,19 @@
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">I8</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT (10)</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -80511,27 +80511,27 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">gNT</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">p15</t>
+          <t xml:space="preserve">p?</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">unknown</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-01-16</t>
+          <t xml:space="preserve">2025-04-24</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t xml:space="preserve">16-01-26</t>
+          <t xml:space="preserve">24-04-25</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
@@ -80541,34 +80541,34 @@
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">I9</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+          <t xml:space="preserve">HEK ATP7B KO g3</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">HEK293T</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">KO</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">DtxR</t>
+          <t xml:space="preserve">Par</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t xml:space="preserve">CASPEX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -80578,22 +80578,22 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">p8</t>
+          <t xml:space="preserve">p+2</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-04-24</t>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t xml:space="preserve">24-04-25</t>
+          <t xml:space="preserve">10/4/2026</t>
         </is>
       </c>
       <c r="K348" t="inlineStr">
@@ -80603,24 +80603,24 @@
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">I9</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+          <t xml:space="preserve">LNCX gNT</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK293T</t>
+          <t xml:space="preserve">LnCap</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t xml:space="preserve">OX</t>
+          <t xml:space="preserve">-</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -80630,32 +80630,32 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">-</t>
+          <t xml:space="preserve">gNT</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t xml:space="preserve">p24</t>
+          <t xml:space="preserve">p+24</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">absolute</t>
+          <t xml:space="preserve">relative</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-07-31</t>
+          <t xml:space="preserve">2026-06-18</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t xml:space="preserve">31-07-26</t>
+          <t xml:space="preserve">18-06-26</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -80665,67 +80665,439 @@
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">I9</t>
+          <t xml:space="preserve">I7</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
+          <t xml:space="preserve">HEK ATP7B-GFP</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p47</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-05-04</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4/5/2026</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuPar50CR+1</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CisR</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P218</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LNCX gP2</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LnCap</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gP2</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p+24</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">relative</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-06-18</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18-06-26</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I8</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT (10)</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gNT</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p15</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16-01-26</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I9</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DuDtxR CASPEX g3</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Du145</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DtxR</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CASPEX</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">g3</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p8</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-04-24</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24-04-25</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I9</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 OX rep2</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK293T</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OX</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">p24</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">absolute</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-07-31</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31-07-26</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I9</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
           <t xml:space="preserve">LNCX gP1</t>
         </is>
       </c>
-      <c r="B350" t="inlineStr">
+      <c r="B356" t="inlineStr">
         <is>
           <t xml:space="preserve">LnCap</t>
         </is>
       </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Par</t>
-        </is>
-      </c>
-      <c r="E350" t="inlineStr">
+      <c r="C356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">-</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Par</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
         <is>
           <t xml:space="preserve">CASPEX</t>
         </is>
       </c>
-      <c r="F350" t="inlineStr">
+      <c r="F356" t="inlineStr">
         <is>
           <t xml:space="preserve">gP1</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr">
+      <c r="G356" t="inlineStr">
         <is>
           <t xml:space="preserve">p+24</t>
         </is>
       </c>
-      <c r="H350" t="inlineStr">
+      <c r="H356" t="inlineStr">
         <is>
           <t xml:space="preserve">relative</t>
         </is>
       </c>
-      <c r="I350" t="inlineStr">
+      <c r="I356" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-06-15</t>
         </is>
       </c>
-      <c r="J350" t="inlineStr">
+      <c r="J356" t="inlineStr">
         <is>
           <t xml:space="preserve">15-06-26</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr">
+      <c r="K356" t="inlineStr">
         <is>
           <t xml:space="preserve">Freezer 1 → Rack 1</t>
         </is>
       </c>
-      <c r="L350" t="inlineStr">
+      <c r="L356" t="inlineStr">
         <is>
           <t xml:space="preserve">I9</t>
         </is>
@@ -80783,17 +81155,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-11</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -80804,33 +81176,23 @@
       <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-10</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Du145</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -80841,23 +81203,13 @@
       <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:29.978Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -80867,7 +81219,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">LUCX</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -80877,14 +81229,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -80894,7 +81246,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -80911,7 +81263,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -80921,7 +81273,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -80931,14 +81283,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
+          <t xml:space="preserve">2026-09-15T08:59:01.686Z</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -80948,7 +81300,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">LNCX</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -80965,12 +81317,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
+          <t xml:space="preserve">2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -80985,24 +81337,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
+          <t xml:space="preserve">2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">Du145</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -81013,13 +81375,23 @@
       <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 F6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
+          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -81029,7 +81401,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -81046,7 +81418,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
+          <t xml:space="preserve">2026-09-09T13:48:02.210Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -81056,7 +81428,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -81073,17 +81445,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -81094,33 +81466,23 @@
       <c r="E12" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:21.749Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -81130,34 +81492,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -81168,33 +81520,23 @@
       <c r="E14" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:19.918Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -81204,29 +81546,19 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -81242,28 +81574,18 @@
       <c r="E16" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-09</t>
+          <t xml:space="preserve">2026-09-09T04:57:16.692Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -81278,17 +81600,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -81305,7 +81617,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -81320,7 +81632,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -81352,12 +81664,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -81389,12 +81701,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -81416,7 +81728,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -81426,12 +81738,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -81453,7 +81765,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -81463,12 +81775,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -81500,12 +81812,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -81527,7 +81839,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">kkk</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -81537,12 +81849,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -81564,7 +81876,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">deneme</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -81579,7 +81891,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -81591,17 +81903,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -81611,24 +81923,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -81639,23 +81961,33 @@
       <c r="E27" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -81665,24 +81997,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -81692,24 +82034,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H3</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">kkk</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -81719,24 +82071,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 H2</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">deneme</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -81747,13 +82109,23 @@
       <c r="E31" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B3</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -81763,7 +82135,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -81773,14 +82145,14 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
+          <t xml:space="preserve">2026-09-08T20:53:21.794Z</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -81790,7 +82162,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -81807,7 +82179,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -81817,7 +82189,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -81834,7 +82206,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -81844,7 +82216,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -81854,14 +82226,14 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -81871,7 +82243,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -81888,7 +82260,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -81898,7 +82270,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -81915,17 +82287,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -81935,34 +82307,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T20:05:13.592Z</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -81972,34 +82334,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -82010,33 +82362,23 @@
       <c r="E40" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T18:36:51.554Z</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -82046,34 +82388,24 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -82084,33 +82416,23 @@
       <c r="E42" t="inlineStr">
         <is>
           <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-08</t>
+          <t xml:space="preserve">2026-09-08T11:09:47.786Z</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">withdrawn</t>
+          <t xml:space="preserve">added</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -82120,17 +82442,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">thaw</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
@@ -82147,7 +82459,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -82162,7 +82474,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -82184,7 +82496,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -82199,7 +82511,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -82221,7 +82533,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -82236,7 +82548,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -82258,7 +82570,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -82273,7 +82585,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -82295,7 +82607,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -82310,7 +82622,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -82332,7 +82644,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -82347,7 +82659,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -82369,7 +82681,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -82384,7 +82696,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -82406,7 +82718,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -82421,7 +82733,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -82443,7 +82755,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -82458,7 +82770,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -82480,7 +82792,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -82495,7 +82807,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -82665,7 +82977,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -82680,7 +82992,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -82717,7 +83029,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -82739,7 +83051,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -82754,7 +83066,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -82776,7 +83088,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -82791,7 +83103,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -82828,7 +83140,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -82865,7 +83177,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -82976,7 +83288,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -82998,7 +83310,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hek caspex</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -83008,12 +83320,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -83035,7 +83347,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -83045,7 +83357,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -83072,7 +83384,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -83082,12 +83394,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -83109,7 +83421,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -83119,12 +83431,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -83146,7 +83458,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -83156,12 +83468,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -83183,7 +83495,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -83193,12 +83505,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -83220,7 +83532,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">Hek caspex</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -83235,7 +83547,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 I8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -83257,7 +83569,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -83272,7 +83584,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -83294,7 +83606,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -83309,7 +83621,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -83331,7 +83643,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">khk</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -83346,7 +83658,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 D4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -83368,7 +83680,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -83383,7 +83695,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -83405,7 +83717,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -83420,7 +83732,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 E8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -83442,7 +83754,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -83457,7 +83769,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 B8</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -83479,7 +83791,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -83494,7 +83806,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D5</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -83516,7 +83828,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -83531,7 +83843,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -83553,7 +83865,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">khk</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -83568,7 +83880,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 D4</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -83738,7 +84050,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -83753,7 +84065,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -83790,7 +84102,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -83812,7 +84124,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t xml:space="preserve">jkl</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -83827,7 +84139,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -83849,7 +84161,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t xml:space="preserve">klm ox</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -83864,7 +84176,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -83901,7 +84213,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -83938,7 +84250,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -84049,7 +84361,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A2</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -84061,17 +84373,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">klm ox</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -84081,24 +84393,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A1</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -84108,24 +84430,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -84136,23 +84468,33 @@
       <c r="E98" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -84163,23 +84505,33 @@
       <c r="E99" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -84189,24 +84541,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A3</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-08</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t xml:space="preserve">added</t>
+          <t xml:space="preserve">withdrawn</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">jkl</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -84216,14 +84578,24 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Freezer 1 → Rack 1 A4</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">thaw</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -84233,7 +84605,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -84243,14 +84615,14 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -84260,7 +84632,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 3xFLAG</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -84270,14 +84642,14 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -84287,7 +84659,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -84297,14 +84669,14 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:21:12.672Z</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -84314,7 +84686,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -84324,14 +84696,14 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -84341,7 +84713,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -84351,14 +84723,14 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -84368,7 +84740,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -84378,14 +84750,14 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -84395,7 +84767,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -84405,14 +84777,14 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:40.838Z</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -84422,7 +84794,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 3xFLAG</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -84432,14 +84804,14 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -84449,7 +84821,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -84459,14 +84831,14 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -84476,7 +84848,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Huh7 gNT</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -84486,14 +84858,14 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -84503,7 +84875,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -84513,14 +84885,14 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:20:16.472Z</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -84530,7 +84902,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">Huh7 ATF3 KO rep3</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -84540,14 +84912,14 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -84557,7 +84929,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 OX rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -84567,14 +84939,14 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -84584,7 +84956,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t xml:space="preserve">hek atf3 ox rep3</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -84594,14 +84966,14 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -84611,7 +84983,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -84621,14 +84993,14 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:46.171Z</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -84638,7 +85010,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">Huh7 gNT</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -84648,14 +85020,14 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -84665,7 +85037,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -84675,14 +85047,14 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -84692,7 +85064,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK 3xFLAG</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -84702,14 +85074,14 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -84719,7 +85091,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK ATF3 OX rep3</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -84729,14 +85101,14 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:19:15.021Z</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -84746,7 +85118,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">hek atf3 ox rep3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -84756,14 +85128,14 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -84773,7 +85145,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -84783,14 +85155,14 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -84800,7 +85172,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -84810,14 +85182,14 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -84827,7 +85199,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -84837,14 +85209,14 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:48.988Z</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -84854,7 +85226,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK 3xFLAG</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -84864,14 +85236,14 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t xml:space="preserve">admin</t>
+          <t xml:space="preserve">umut</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -84881,7 +85253,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t xml:space="preserve">HEK gNT</t>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -84891,32 +85263,194 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t xml:space="preserve">umut</t>
+          <t xml:space="preserve">admin</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:18:16.654Z</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK ATF3 KO rep2</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t xml:space="preserve">added</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t xml:space="preserve">HEK gNT</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t xml:space="preserve">unknown device</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">admin</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">umut</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-07T15:17:40.188Z</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">added</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HEK gNT</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unknown device</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
         <is>
           <t xml:space="preserve">umut</t>
         </is>
